--- a/2024-09-20018D Source Data Fig. 4.xlsx
+++ b/2024-09-20018D Source Data Fig. 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/google drive KE version/older files/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755FEA80-E1DC-4469-BC28-9EA497084005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3319B534-64D2-E949-827D-034B6DFAC13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="880" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 4b" sheetId="9" r:id="rId1"/>
@@ -85,13 +85,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -115,14 +115,15 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -197,15 +198,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -479,34 +480,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CAB82F2-6DB0-4572-B336-3FBFCFA17A93}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1.282</v>
       </c>
@@ -550,17 +551,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8917E4FF-3BAD-420A-864D-59D42E1F9FC2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -568,7 +569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>30.6</v>
       </c>
@@ -576,7 +577,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>18.8</v>
       </c>
@@ -594,49 +595,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56D3632-B209-4391-AB20-B1659E0EB72F}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7" t="s">
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1.1599999999999999</v>
       </c>
@@ -659,7 +660,7 @@
         <v>0.03</v>
       </c>
       <c r="H3" s="5">
-        <v>2.4279716999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I3" s="2">
         <v>0.03</v>
@@ -710,17 +711,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFB45FD-7CE4-439C-93E0-F61F978CD624}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -728,7 +729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>9.9</v>
       </c>
@@ -736,7 +737,7 @@
         <v>61.36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>13.5</v>
       </c>
@@ -754,17 +755,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -772,24 +773,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="8">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
         <v>0.85</v>
       </c>
       <c r="B3" s="2">
         <v>12.49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="8">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>0.79</v>
       </c>
       <c r="B4" s="2">
         <v>11.76</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="8">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>2.29</v>
       </c>
       <c r="B5" s="2">
@@ -806,39 +807,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B423DA5D-02AC-4900-9F4A-064528526248}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.64453125" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1.1200000000000001</v>
       </c>

--- a/2024-09-20018D Source Data Fig. 4.xlsx
+++ b/2024-09-20018D Source Data Fig. 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hw/hfgwang drive/学生总结/郜艳敏/KNIT version/google drive KE version/older files/B. 2024-09-20018D KNIT editing All /Updated KE files 2024-09-20018D /KE Source Data Excels (updated KE version)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3319B534-64D2-E949-827D-034B6DFAC13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755FEA80-E1DC-4469-BC28-9EA497084005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="880" windowWidth="21800" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 4b" sheetId="9" r:id="rId1"/>
@@ -85,13 +85,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -115,15 +115,14 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="4"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -198,15 +197,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -480,34 +479,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CAB82F2-6DB0-4572-B336-3FBFCFA17A93}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1.282</v>
       </c>
@@ -551,17 +550,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8917E4FF-3BAD-420A-864D-59D42E1F9FC2}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -569,7 +568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>30.6</v>
       </c>
@@ -577,7 +576,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>18.8</v>
       </c>
@@ -595,49 +594,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56D3632-B209-4391-AB20-B1659E0EB72F}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8" t="s">
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1.1599999999999999</v>
       </c>
@@ -660,7 +659,7 @@
         <v>0.03</v>
       </c>
       <c r="H3" s="5">
-        <v>0.02</v>
+        <v>2.4279716999999999E-2</v>
       </c>
       <c r="I3" s="2">
         <v>0.03</v>
@@ -711,17 +710,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFB45FD-7CE4-439C-93E0-F61F978CD624}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -729,7 +728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="6">
         <v>9.9</v>
       </c>
@@ -737,7 +736,7 @@
         <v>61.36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>13.5</v>
       </c>
@@ -755,17 +754,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -773,24 +772,24 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="8">
         <v>0.85</v>
       </c>
       <c r="B3" s="2">
         <v>12.49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="8">
         <v>0.79</v>
       </c>
       <c r="B4" s="2">
         <v>11.76</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="8">
         <v>2.29</v>
       </c>
       <c r="B5" s="2">
@@ -807,39 +806,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B423DA5D-02AC-4900-9F4A-064528526248}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1.1200000000000001</v>
       </c>
@@ -888,4 +887,262 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A580DDD6E32D24793B52EBDA382135E" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="420b5df69e2a8ef095a347c37071042d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="03670651-1d3f-4393-a695-0ad38e7dc27c" xmlns:ns3="98cfd510-5244-40a7-ac81-0d7d1b58424e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43051459d3b7bcd6c9644565fa79aaf6" ns2:_="" ns3:_="">
+    <xsd:import namespace="03670651-1d3f-4393-a695-0ad38e7dc27c"/>
+    <xsd:import namespace="98cfd510-5244-40a7-ac81-0d7d1b58424e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationSourceID" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:ArchiverLinkFileType" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="03670651-1d3f-4393-a695-0ad38e7dc27c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationSourceID" ma:index="8" nillable="true" ma:displayName="MigrationSourceID" ma:internalName="MigrationSourceID" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fe026092-a6d1-42a7-a35d-9d1bdd270ae7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="03670651-1d3f-4393-a695-0ad38e7dc27c">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="98cfd510-5244-40a7-ac81-0d7d1b58424e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fb58666-e629-4e5a-b780-b8dcc15b318b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ArchiverLinkFileType" ma:index="23" nillable="true" ma:displayName="ArchiverLinkFileType" ma:hidden="true" ma:internalName="ArchiverLinkFileType">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="03670651-1d3f-4393-a695-0ad38e7dc27c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ArchiverLinkFileType xmlns="98cfd510-5244-40a7-ac81-0d7d1b58424e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7773740F-E86F-497F-8269-5DD847C93691}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4608F05-D9EF-4527-9D36-F81AD04472A7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31D4E91B-11ED-4E59-960C-C84EDE69ED74}"/>
 </file>